--- a/EndResult/200m Medley.xlsx
+++ b/EndResult/200m Medley.xlsx
@@ -677,12 +677,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christian Tronvoll</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.14,69</t>
+          <t>2.14,67</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -690,12 +690,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18.01.2014</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -712,12 +712,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Christian Tronvoll</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.14,67</t>
+          <t>2.14,69</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -725,12 +725,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>18.01.2014</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -973,12 +973,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Tudor Ignat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.18,49</t>
+          <t>2.18,54</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.05.2021</t>
+          <t>08.08.2023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Funchal</t>
+          <t>Kyushu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1008,12 +1008,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tudor Ignat</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.18,54</t>
+          <t>2.18,49</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08.08.2023</t>
+          <t>22.05.2021</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kyushu</t>
+          <t>Funchal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/EndResult/200m Medley.xlsx
+++ b/EndResult/200m Medley.xlsx
@@ -677,12 +677,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Christian Tronvoll</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.14,67</t>
+          <t>2.14,69</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -690,12 +690,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>18.01.2014</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -712,12 +712,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Christian Tronvoll</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.14,69</t>
+          <t>2.14,67</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -725,12 +725,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.01.2014</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -973,12 +973,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tudor Ignat</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.18,54</t>
+          <t>2.18,49</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08.08.2023</t>
+          <t>22.05.2021</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kyushu</t>
+          <t>Funchal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1008,12 +1008,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Tudor Ignat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.18,49</t>
+          <t>2.18,54</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.05.2021</t>
+          <t>08.08.2023</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Funchal</t>
+          <t>Kyushu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1479,25 +1479,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monica Martinsen</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.30,08</t>
+          <t>2.29,56</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25.01.2008</t>
+          <t>12.04.2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1514,25 +1514,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Monica Martinsen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.30,62</t>
+          <t>2.30,08</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.02.2012</t>
+          <t>25.01.2008</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1549,25 +1549,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karoline Volden</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.31,90</t>
+          <t>2.30,62</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>03.04.2016</t>
+          <t>12.02.2012</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mandal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1584,25 +1584,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Karoline Volden</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.31,95</t>
+          <t>2.31,90</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>03.04.2016</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Mandal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1705,25 +1705,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Henriette Martinsen</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.27,88</t>
+          <t>2.25,87</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08.06.2007</t>
+          <t>22.03.2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1740,25 +1740,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maria Erikovna Alvestad</t>
+          <t>Henriette Martinsen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.28,35</t>
+          <t>2.27,88</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.01.2025</t>
+          <t>08.06.2007</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1845,25 +1845,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.35,26</t>
+          <t>2.33,29</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06.03.2016</t>
+          <t>04.07.2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1880,25 +1880,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.35,46</t>
+          <t>2.35,26</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14.04.2018</t>
+          <t>06.03.2016</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1915,25 +1915,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Christiana Bjørkli</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.37,74</t>
+          <t>2.35,46</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04.11.2007</t>
+          <t>14.04.2018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1950,20 +1950,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stine Tveit</t>
+          <t>Christiana Bjørkli</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.38,97</t>
+          <t>2.37,74</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01.11.2008</t>
+          <t>04.11.2007</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1985,25 +1985,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Julie Mathilde Bjordal</t>
+          <t>Stine Tveit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.40,35</t>
+          <t>2.38,97</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06.05.2017</t>
+          <t>01.11.2008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
